--- a/docs/kp.xlsx
+++ b/docs/kp.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="F22" s="11">
         <f>IF(OR(C22="",E22=""),"",C22*E22)</f>
-        <v/>
+        <v>49950</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -774,7 +774,7 @@
       </c>
       <c r="F23" s="11">
         <f>IF(OR(C23="",E23=""),"",C23*E23)</f>
-        <v/>
+        <v>49000</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -799,7 +799,7 @@
       </c>
       <c r="F24" s="11">
         <f>IF(OR(C24="",E24=""),"",C24*E24)</f>
-        <v/>
+        <v>13000</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -824,7 +824,7 @@
       </c>
       <c r="F25" s="11">
         <f>IF(OR(C25="",E25=""),"",C25*E25)</f>
-        <v/>
+        <v>19000</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -849,7 +849,7 @@
       </c>
       <c r="F26" s="11">
         <f>IF(OR(C26="",E26=""),"",C26*E26)</f>
-        <v/>
+        <v>16000</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -874,7 +874,7 @@
       </c>
       <c r="F27" s="11">
         <f>IF(OR(C27="",E27=""),"",C27*E27)</f>
-        <v/>
+        <v>18000</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -899,7 +899,7 @@
       </c>
       <c r="F28" s="11">
         <f>IF(OR(C28="",E28=""),"",C28*E28)</f>
-        <v/>
+        <v>7000</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -910,7 +910,7 @@
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11">
+      <c r="F29" s="11" t="str">
         <f>IF(OR(C29="",E29=""),"",C29*E29)</f>
         <v/>
       </c>
@@ -923,7 +923,7 @@
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11">
+      <c r="F30" s="11" t="str">
         <f>IF(OR(C30="",E30=""),"",C30*E30)</f>
         <v/>
       </c>
@@ -936,7 +936,7 @@
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11">
+      <c r="F31" s="11" t="str">
         <f>IF(OR(C31="",E31=""),"",C31*E31)</f>
         <v/>
       </c>
@@ -949,7 +949,7 @@
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11">
+      <c r="F32" s="11" t="str">
         <f>IF(OR(C32="",E32=""),"",C32*E32)</f>
         <v/>
       </c>
@@ -962,7 +962,7 @@
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11">
+      <c r="F33" s="11" t="str">
         <f>IF(OR(C33="",E33=""),"",C33*E33)</f>
         <v/>
       </c>
@@ -975,13 +975,13 @@
       </c>
       <c r="F34" s="13">
         <f>SUM(F22:F33)</f>
-        <v/>
+        <v>171950</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14">
+      <c r="A36" s="14" t="str">
         <f>"Всего наименований "&amp;COUNTA(B22:B33)&amp;", на сумму "&amp;TEXT(F34,"#,##0.00")&amp;" ₽"</f>
-        <v/>
+        <v>Всего наименований 7, на сумму 171 950,00 ₽</v>
       </c>
     </row>
     <row r="37">
